--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/119.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/119.xlsx
@@ -426,13 +426,13 @@
         <v>-22.05144515866132</v>
       </c>
       <c r="E2">
-        <v>-12.52521323656888</v>
+        <v>-15.6032623043225</v>
       </c>
       <c r="F2">
-        <v>-4.562121788566407</v>
+        <v>-5.659093948662875</v>
       </c>
       <c r="G2">
-        <v>-9.622856564942992</v>
+        <v>-10.53500124574177</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-22.12852529880933</v>
       </c>
       <c r="E3">
-        <v>-14.31101696149369</v>
+        <v>-15.83491639218488</v>
       </c>
       <c r="F3">
-        <v>-4.201897111417611</v>
+        <v>-5.481608777306455</v>
       </c>
       <c r="G3">
-        <v>-7.978561564315623</v>
+        <v>-11.1167303079025</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-22.16073918336937</v>
       </c>
       <c r="E4">
-        <v>-12.22018428436022</v>
+        <v>-15.78691909617758</v>
       </c>
       <c r="F4">
-        <v>-4.573881292216549</v>
+        <v>-5.190025936623238</v>
       </c>
       <c r="G4">
-        <v>-8.877176045495395</v>
+        <v>-10.89126560395043</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-22.11850990087945</v>
       </c>
       <c r="E5">
-        <v>-13.53403044820562</v>
+        <v>-17.06089657485945</v>
       </c>
       <c r="F5">
-        <v>-4.406102101718731</v>
+        <v>-5.384945756706379</v>
       </c>
       <c r="G5">
-        <v>-8.189870375541764</v>
+        <v>-10.81615594675545</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-21.98138085376352</v>
       </c>
       <c r="E6">
-        <v>-15.36579818430828</v>
+        <v>-18.24954401781479</v>
       </c>
       <c r="F6">
-        <v>-4.634347142416495</v>
+        <v>-5.172256627465786</v>
       </c>
       <c r="G6">
-        <v>-9.436585409630361</v>
+        <v>-11.44281242242963</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-21.74088535431892</v>
       </c>
       <c r="E7">
-        <v>-14.25109619342419</v>
+        <v>-18.21658578398696</v>
       </c>
       <c r="F7">
-        <v>-4.653296875122938</v>
+        <v>-5.336199648521238</v>
       </c>
       <c r="G7">
-        <v>-8.721798901155239</v>
+        <v>-11.26550291389181</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-21.39253633463023</v>
       </c>
       <c r="E8">
-        <v>-15.66215510879225</v>
+        <v>-18.08417320400268</v>
       </c>
       <c r="F8">
-        <v>-4.809291710948529</v>
+        <v>-4.844671282722096</v>
       </c>
       <c r="G8">
-        <v>-8.818629047633383</v>
+        <v>-11.16561051278984</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-20.91773850382926</v>
       </c>
       <c r="E9">
-        <v>-17.80650982022238</v>
+        <v>-18.59907881257083</v>
       </c>
       <c r="F9">
-        <v>-4.041480450395876</v>
+        <v>-4.694319285644374</v>
       </c>
       <c r="G9">
-        <v>-7.989132136222516</v>
+        <v>-10.11606163938361</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-20.31082529806304</v>
       </c>
       <c r="E10">
-        <v>-17.7247572789619</v>
+        <v>-19.50407622910772</v>
       </c>
       <c r="F10">
-        <v>-4.312379785398592</v>
+        <v>-4.89322355293498</v>
       </c>
       <c r="G10">
-        <v>-8.386950462040117</v>
+        <v>-10.80752535453457</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-19.57447305476646</v>
       </c>
       <c r="E11">
-        <v>-18.89173597379054</v>
+        <v>-21.01412305780945</v>
       </c>
       <c r="F11">
-        <v>-4.190960176598449</v>
+        <v>-4.6256194634606</v>
       </c>
       <c r="G11">
-        <v>-7.265519713339698</v>
+        <v>-11.08512452963908</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-18.71309300511448</v>
       </c>
       <c r="E12">
-        <v>-17.99399317261394</v>
+        <v>-19.84448614873831</v>
       </c>
       <c r="F12">
-        <v>-4.3871258612554</v>
+        <v>-4.920006327802295</v>
       </c>
       <c r="G12">
-        <v>-7.795730065818293</v>
+        <v>-10.02462768213448</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-17.72685526400948</v>
       </c>
       <c r="E13">
-        <v>-18.75535192210153</v>
+        <v>-21.43441525893535</v>
       </c>
       <c r="F13">
-        <v>-4.344850130853527</v>
+        <v>-4.917889020720739</v>
       </c>
       <c r="G13">
-        <v>-7.419893762381453</v>
+        <v>-9.864966691866513</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-16.64973423001418</v>
       </c>
       <c r="E14">
-        <v>-19.96493450039433</v>
+        <v>-21.81869250627824</v>
       </c>
       <c r="F14">
-        <v>-3.907769526072994</v>
+        <v>-4.805255076594687</v>
       </c>
       <c r="G14">
-        <v>-6.65619725410914</v>
+        <v>-9.311238223876936</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.51677687697073</v>
       </c>
       <c r="E15">
-        <v>-20.17555382649108</v>
+        <v>-22.90047701960057</v>
       </c>
       <c r="F15">
-        <v>-3.443921885405799</v>
+        <v>-4.543968945301459</v>
       </c>
       <c r="G15">
-        <v>-7.441938685127459</v>
+        <v>-8.057180399782235</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-14.3614031947129</v>
       </c>
       <c r="E16">
-        <v>-21.3173768482071</v>
+        <v>-23.49160137419182</v>
       </c>
       <c r="F16">
-        <v>-3.740320854168893</v>
+        <v>-4.365596592456641</v>
       </c>
       <c r="G16">
-        <v>-6.158191888636575</v>
+        <v>-8.048291585009292</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-13.23304887067259</v>
       </c>
       <c r="E17">
-        <v>-21.66709731039746</v>
+        <v>-25.58238876658521</v>
       </c>
       <c r="F17">
-        <v>-2.967251117343269</v>
+        <v>-4.167308630513718</v>
       </c>
       <c r="G17">
-        <v>-5.141500179707618</v>
+        <v>-8.008263778893964</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-12.18451781143098</v>
       </c>
       <c r="E18">
-        <v>-23.58195348759286</v>
+        <v>-25.50141512285406</v>
       </c>
       <c r="F18">
-        <v>-3.156918259725257</v>
+        <v>-4.067346222548291</v>
       </c>
       <c r="G18">
-        <v>-4.989089284170651</v>
+        <v>-8.440710411052342</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.25669213865385</v>
       </c>
       <c r="E19">
-        <v>-24.84402560810856</v>
+        <v>-25.96328777231838</v>
       </c>
       <c r="F19">
-        <v>-3.027123856482811</v>
+        <v>-4.279859737899489</v>
       </c>
       <c r="G19">
-        <v>-4.891606960221273</v>
+        <v>-8.055207314640828</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-10.47033606110504</v>
       </c>
       <c r="E20">
-        <v>-23.65237125841213</v>
+        <v>-26.0223390733784</v>
       </c>
       <c r="F20">
-        <v>-3.167622423304232</v>
+        <v>-3.754957277808958</v>
       </c>
       <c r="G20">
-        <v>-5.171629454660525</v>
+        <v>-7.908109844694392</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.851847337464864</v>
       </c>
       <c r="E21">
-        <v>-26.73255323742336</v>
+        <v>-27.16366849142759</v>
       </c>
       <c r="F21">
-        <v>-2.651397940125428</v>
+        <v>-3.690869805323971</v>
       </c>
       <c r="G21">
-        <v>-5.691020944316782</v>
+        <v>-7.110109463544151</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.404631224822742</v>
       </c>
       <c r="E22">
-        <v>-24.44124954444434</v>
+        <v>-28.3632793699555</v>
       </c>
       <c r="F22">
-        <v>-2.509245123600616</v>
+        <v>-3.494651933520644</v>
       </c>
       <c r="G22">
-        <v>-4.146489233515349</v>
+        <v>-7.166521159533333</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.109722769424186</v>
       </c>
       <c r="E23">
-        <v>-25.87019140366869</v>
+        <v>-29.01668382757424</v>
       </c>
       <c r="F23">
-        <v>-2.683308309216071</v>
+        <v>-3.411946903657738</v>
       </c>
       <c r="G23">
-        <v>-4.193131509618141</v>
+        <v>-7.351908399186979</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.945347416206694</v>
       </c>
       <c r="E24">
-        <v>-27.27089369898121</v>
+        <v>-29.09104137078019</v>
       </c>
       <c r="F24">
-        <v>-2.501197534282419</v>
+        <v>-3.363522202024885</v>
       </c>
       <c r="G24">
-        <v>-5.104498212215185</v>
+        <v>-6.909722142052066</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.882319195210229</v>
       </c>
       <c r="E25">
-        <v>-26.92169401130173</v>
+        <v>-29.08175799906446</v>
       </c>
       <c r="F25">
-        <v>-2.54395206104311</v>
+        <v>-2.840830654532425</v>
       </c>
       <c r="G25">
-        <v>-4.786669287717454</v>
+        <v>-7.820191686807967</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.883937678596432</v>
       </c>
       <c r="E26">
-        <v>-27.49430596414962</v>
+        <v>-29.96205711836352</v>
       </c>
       <c r="F26">
-        <v>-2.312576619930166</v>
+        <v>-2.913492558003789</v>
       </c>
       <c r="G26">
-        <v>-4.591525870359574</v>
+        <v>-7.267645083575911</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.912396227376616</v>
       </c>
       <c r="E27">
-        <v>-26.98657798688363</v>
+        <v>-29.97060008457899</v>
       </c>
       <c r="F27">
-        <v>-2.35164822521801</v>
+        <v>-2.929948076460401</v>
       </c>
       <c r="G27">
-        <v>-5.31324135064839</v>
+        <v>-6.526648986066379</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.948072011298095</v>
       </c>
       <c r="E28">
-        <v>-27.13627122368118</v>
+        <v>-29.89384245014897</v>
       </c>
       <c r="F28">
-        <v>-1.796276755317707</v>
+        <v>-3.275065817284343</v>
       </c>
       <c r="G28">
-        <v>-4.237578894028396</v>
+        <v>-7.451479677371639</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.97647079328906</v>
       </c>
       <c r="E29">
-        <v>-28.68331568502558</v>
+        <v>-28.69203752596435</v>
       </c>
       <c r="F29">
-        <v>-1.86911592941327</v>
+        <v>-3.044184083143467</v>
       </c>
       <c r="G29">
-        <v>-5.564501825442456</v>
+        <v>-7.285022137111545</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-8.984615495592642</v>
       </c>
       <c r="E30">
-        <v>-27.16753580823014</v>
+        <v>-29.61253364479249</v>
       </c>
       <c r="F30">
-        <v>-1.937625227094401</v>
+        <v>-2.988500397959881</v>
       </c>
       <c r="G30">
-        <v>-4.593783662417358</v>
+        <v>-7.311840866525181</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-8.970468105298384</v>
       </c>
       <c r="E31">
-        <v>-28.11044560915925</v>
+        <v>-30.55468719056232</v>
       </c>
       <c r="F31">
-        <v>-2.815057659529124</v>
+        <v>-2.780591777000845</v>
       </c>
       <c r="G31">
-        <v>-4.767418465406593</v>
+        <v>-7.938649627294169</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-8.940196161005259</v>
       </c>
       <c r="E32">
-        <v>-27.48106017767719</v>
+        <v>-29.79772332509917</v>
       </c>
       <c r="F32">
-        <v>-1.675596050240861</v>
+        <v>-2.922070302459778</v>
       </c>
       <c r="G32">
-        <v>-3.871071707921222</v>
+        <v>-7.194157593695168</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.902397214601653</v>
       </c>
       <c r="E33">
-        <v>-28.13922406147799</v>
+        <v>-29.31038706628971</v>
       </c>
       <c r="F33">
-        <v>-2.432594631084772</v>
+        <v>-2.681635007062416</v>
       </c>
       <c r="G33">
-        <v>-5.001000627020949</v>
+        <v>-7.5116157370925</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-8.863016570512016</v>
       </c>
       <c r="E34">
-        <v>-27.36988614078888</v>
+        <v>-29.31496988198548</v>
       </c>
       <c r="F34">
-        <v>-1.908782302496325</v>
+        <v>-2.534151646300589</v>
       </c>
       <c r="G34">
-        <v>-5.268075577856113</v>
+        <v>-6.829626803274939</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-8.832014428247263</v>
       </c>
       <c r="E35">
-        <v>-27.8289828356865</v>
+        <v>-29.54830856217871</v>
       </c>
       <c r="F35">
-        <v>-1.768610112431606</v>
+        <v>-2.647620584768662</v>
       </c>
       <c r="G35">
-        <v>-5.325751902241295</v>
+        <v>-7.702786499803254</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-8.820647810362617</v>
       </c>
       <c r="E36">
-        <v>-25.32325136997028</v>
+        <v>-29.35656391574593</v>
       </c>
       <c r="F36">
-        <v>-2.324982250154491</v>
+        <v>-2.566699029923984</v>
       </c>
       <c r="G36">
-        <v>-5.550408833081778</v>
+        <v>-7.413371987669088</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-8.831273875393808</v>
       </c>
       <c r="E37">
-        <v>-26.77459106163657</v>
+        <v>-28.67690336583071</v>
       </c>
       <c r="F37">
-        <v>-2.149737812622645</v>
+        <v>-2.799938297693227</v>
       </c>
       <c r="G37">
-        <v>-6.631162908741171</v>
+        <v>-8.184510602313683</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-8.864431172225842</v>
       </c>
       <c r="E38">
-        <v>-24.55495046982893</v>
+        <v>-28.61985365028209</v>
       </c>
       <c r="F38">
-        <v>-1.764107935597391</v>
+        <v>-3.000900229612387</v>
       </c>
       <c r="G38">
-        <v>-6.239445918352447</v>
+        <v>-7.972086137240808</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.921800168553853</v>
       </c>
       <c r="E39">
-        <v>-25.18522348221649</v>
+        <v>-27.63558982471493</v>
       </c>
       <c r="F39">
-        <v>-1.685128902312278</v>
+        <v>-2.818438226899949</v>
       </c>
       <c r="G39">
-        <v>-5.54195038922894</v>
+        <v>-7.00754876273753</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.001262190270273</v>
       </c>
       <c r="E40">
-        <v>-26.16947372236162</v>
+        <v>-27.04162158844687</v>
       </c>
       <c r="F40">
-        <v>-2.088570335232526</v>
+        <v>-2.365994720267095</v>
       </c>
       <c r="G40">
-        <v>-4.757006799685584</v>
+        <v>-7.791512430801261</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.094945747876054</v>
       </c>
       <c r="E41">
-        <v>-24.61366666381238</v>
+        <v>-27.22589425276699</v>
       </c>
       <c r="F41">
-        <v>-2.249153498102225</v>
+        <v>-2.444366560245956</v>
       </c>
       <c r="G41">
-        <v>-5.029782509939373</v>
+        <v>-7.579174039912408</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.198105378581362</v>
       </c>
       <c r="E42">
-        <v>-25.30799494103844</v>
+        <v>-26.95312614938897</v>
       </c>
       <c r="F42">
-        <v>-1.575039702847626</v>
+        <v>-2.602234334769277</v>
       </c>
       <c r="G42">
-        <v>-6.135044554225991</v>
+        <v>-8.63349671998626</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-9.309328455196727</v>
       </c>
       <c r="E43">
-        <v>-22.7065541771701</v>
+        <v>-27.26866116129543</v>
       </c>
       <c r="F43">
-        <v>-1.469711959214266</v>
+        <v>-2.170997862015494</v>
       </c>
       <c r="G43">
-        <v>-5.500167993977798</v>
+        <v>-7.62831246735181</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-9.420614139665458</v>
       </c>
       <c r="E44">
-        <v>-22.58237436293177</v>
+        <v>-25.18861078077422</v>
       </c>
       <c r="F44">
-        <v>-2.159263209387436</v>
+        <v>-2.655569598365926</v>
       </c>
       <c r="G44">
-        <v>-5.038389928341478</v>
+        <v>-7.808816652335032</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-9.525805854593628</v>
       </c>
       <c r="E45">
-        <v>-23.01442701105558</v>
+        <v>-25.42361593940228</v>
       </c>
       <c r="F45">
-        <v>-1.956277575903237</v>
+        <v>-2.276574115869694</v>
       </c>
       <c r="G45">
-        <v>-5.293838243242721</v>
+        <v>-7.509228833758685</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-9.623330688401115</v>
       </c>
       <c r="E46">
-        <v>-22.69588056393402</v>
+        <v>-23.55600533152891</v>
       </c>
       <c r="F46">
-        <v>-1.183704031151889</v>
+        <v>-2.332519565152564</v>
       </c>
       <c r="G46">
-        <v>-6.095294833935962</v>
+        <v>-7.222843470792953</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-9.709746090542778</v>
       </c>
       <c r="E47">
-        <v>-21.20416499801534</v>
+        <v>-23.56075117228895</v>
       </c>
       <c r="F47">
-        <v>-1.524039606959469</v>
+        <v>-2.266954285220983</v>
       </c>
       <c r="G47">
-        <v>-4.856104669858128</v>
+        <v>-7.990638434442884</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-9.778070596261472</v>
       </c>
       <c r="E48">
-        <v>-20.95430644464213</v>
+        <v>-23.38952957005893</v>
       </c>
       <c r="F48">
-        <v>-1.917532347372096</v>
+        <v>-2.678584958285308</v>
       </c>
       <c r="G48">
-        <v>-4.895675620689037</v>
+        <v>-7.982696435694172</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-9.825423270346786</v>
       </c>
       <c r="E49">
-        <v>-19.72633826187819</v>
+        <v>-23.95512691666894</v>
       </c>
       <c r="F49">
-        <v>-1.735131643847464</v>
+        <v>-2.530706466272346</v>
       </c>
       <c r="G49">
-        <v>-7.145154898622876</v>
+        <v>-8.008697460359608</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-9.851873608356424</v>
       </c>
       <c r="E50">
-        <v>-19.23211419410307</v>
+        <v>-22.56311929145115</v>
       </c>
       <c r="F50">
-        <v>-1.772578820658419</v>
+        <v>-2.184417413940846</v>
       </c>
       <c r="G50">
-        <v>-6.251042759376514</v>
+        <v>-8.411061165202629</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.851572068746032</v>
       </c>
       <c r="E51">
-        <v>-19.94126869523024</v>
+        <v>-22.08020735174719</v>
       </c>
       <c r="F51">
-        <v>-1.602685636548657</v>
+        <v>-2.545592228500653</v>
       </c>
       <c r="G51">
-        <v>-5.562690957032474</v>
+        <v>-7.046722448103726</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.821894663277343</v>
       </c>
       <c r="E52">
-        <v>-17.73656753917391</v>
+        <v>-21.14236038475866</v>
       </c>
       <c r="F52">
-        <v>-1.88938773649458</v>
+        <v>-2.650018708399767</v>
       </c>
       <c r="G52">
-        <v>-6.51538319959624</v>
+        <v>-8.26810849827136</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.764075923452046</v>
       </c>
       <c r="E53">
-        <v>-19.5770344738453</v>
+        <v>-20.58276779468282</v>
       </c>
       <c r="F53">
-        <v>-1.784203300421904</v>
+        <v>-2.365572252891667</v>
       </c>
       <c r="G53">
-        <v>-6.075908279257989</v>
+        <v>-8.416646055527378</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.676744968658355</v>
       </c>
       <c r="E54">
-        <v>-17.90410749203569</v>
+        <v>-21.3043846562791</v>
       </c>
       <c r="F54">
-        <v>-2.01886073318474</v>
+        <v>-2.479820685085775</v>
       </c>
       <c r="G54">
-        <v>-7.039061845725852</v>
+        <v>-9.19633580929991</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.556770890913368</v>
       </c>
       <c r="E55">
-        <v>-17.88064999667596</v>
+        <v>-20.17813052820144</v>
       </c>
       <c r="F55">
-        <v>-1.365406420955961</v>
+        <v>-2.47206385272596</v>
       </c>
       <c r="G55">
-        <v>-8.107093494877827</v>
+        <v>-8.767289107410365</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.406998255375363</v>
       </c>
       <c r="E56">
-        <v>-16.900045178107</v>
+        <v>-19.78709679763911</v>
       </c>
       <c r="F56">
-        <v>-2.069499660885276</v>
+        <v>-2.332477318415021</v>
       </c>
       <c r="G56">
-        <v>-5.331876411488947</v>
+        <v>-7.817751814745525</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.231877966116235</v>
       </c>
       <c r="E57">
-        <v>-15.2660359019193</v>
+        <v>-19.21219343694333</v>
       </c>
       <c r="F57">
-        <v>-1.446793518281012</v>
+        <v>-2.71803761257844</v>
       </c>
       <c r="G57">
-        <v>-6.78356387264152</v>
+        <v>-9.502783078233627</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.030969505664453</v>
       </c>
       <c r="E58">
-        <v>-16.34259908471079</v>
+        <v>-18.02501774804049</v>
       </c>
       <c r="F58">
-        <v>-1.318644252700526</v>
+        <v>-2.570334734454871</v>
       </c>
       <c r="G58">
-        <v>-5.812690113976076</v>
+        <v>-9.191528897176889</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.809726161275522</v>
       </c>
       <c r="E59">
-        <v>-15.44979232020255</v>
+        <v>-18.30682921401182</v>
       </c>
       <c r="F59">
-        <v>-1.768982877762866</v>
+        <v>-2.219508713858239</v>
       </c>
       <c r="G59">
-        <v>-7.086660869489494</v>
+        <v>-8.782994335448668</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.576249751364777</v>
       </c>
       <c r="E60">
-        <v>-14.43078151357455</v>
+        <v>-18.42202000734493</v>
       </c>
       <c r="F60">
-        <v>-1.199459579153136</v>
+        <v>-2.649096735480451</v>
       </c>
       <c r="G60">
-        <v>-6.649288145568681</v>
+        <v>-8.695960093221228</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.335345353251276</v>
       </c>
       <c r="E61">
-        <v>-15.34159801921129</v>
+        <v>-16.88713449871113</v>
       </c>
       <c r="F61">
-        <v>-1.568686953235557</v>
+        <v>-2.644443795778926</v>
       </c>
       <c r="G61">
-        <v>-6.167765986336147</v>
+        <v>-8.798411546025054</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.090552924040704</v>
       </c>
       <c r="E62">
-        <v>-14.0536728405858</v>
+        <v>-17.72083109199725</v>
       </c>
       <c r="F62">
-        <v>-1.549475456429831</v>
+        <v>-2.549972635326657</v>
       </c>
       <c r="G62">
-        <v>-7.30130340007368</v>
+        <v>-8.750501330980722</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.849908610748551</v>
       </c>
       <c r="E63">
-        <v>-13.03971128247634</v>
+        <v>-17.80499730990381</v>
       </c>
       <c r="F63">
-        <v>-2.66048264543193</v>
+        <v>-2.731108421827213</v>
       </c>
       <c r="G63">
-        <v>-7.125672338124265</v>
+        <v>-9.427656868310946</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.620293413471665</v>
       </c>
       <c r="E64">
-        <v>-14.01678389131931</v>
+        <v>-17.48765090839429</v>
       </c>
       <c r="F64">
-        <v>-2.514703236417662</v>
+        <v>-2.30046671686864</v>
       </c>
       <c r="G64">
-        <v>-7.559472983408204</v>
+        <v>-9.007393043737087</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.402515985353511</v>
       </c>
       <c r="E65">
-        <v>-14.32462049741273</v>
+        <v>-16.83822245095428</v>
       </c>
       <c r="F65">
-        <v>-1.50134151175536</v>
+        <v>-2.918509979362546</v>
       </c>
       <c r="G65">
-        <v>-6.716207513099508</v>
+        <v>-9.231970521484627</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.202107894274054</v>
       </c>
       <c r="E66">
-        <v>-13.55066806170981</v>
+        <v>-16.68037796094293</v>
       </c>
       <c r="F66">
-        <v>-1.994025450081408</v>
+        <v>-2.646392115910311</v>
       </c>
       <c r="G66">
-        <v>-7.743483036117515</v>
+        <v>-8.700190970420417</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.02561590044954</v>
       </c>
       <c r="E67">
-        <v>-12.61959116336274</v>
+        <v>-15.69823346121136</v>
       </c>
       <c r="F67">
-        <v>-1.813314616058487</v>
+        <v>-2.936222131169205</v>
       </c>
       <c r="G67">
-        <v>-6.68817381347296</v>
+        <v>-9.591194507405403</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.875197783785195</v>
       </c>
       <c r="E68">
-        <v>-14.08606954363667</v>
+        <v>-15.6409844928064</v>
       </c>
       <c r="F68">
-        <v>-2.481315888247828</v>
+        <v>-2.838068877611491</v>
       </c>
       <c r="G68">
-        <v>-7.224548401745678</v>
+        <v>-9.225240182403288</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.75157646872392</v>
       </c>
       <c r="E69">
-        <v>-14.53643986912151</v>
+        <v>-16.18230469026129</v>
       </c>
       <c r="F69">
-        <v>-1.692825263851688</v>
+        <v>-2.74943522224675</v>
       </c>
       <c r="G69">
-        <v>-6.411779676944748</v>
+        <v>-9.681708132994617</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.658243139902076</v>
       </c>
       <c r="E70">
-        <v>-13.05965015353211</v>
+        <v>-15.72068563534139</v>
       </c>
       <c r="F70">
-        <v>-2.260140963332957</v>
+        <v>-2.903523156311097</v>
       </c>
       <c r="G70">
-        <v>-8.004973096627928</v>
+        <v>-8.932859421465935</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.597701936087464</v>
       </c>
       <c r="E71">
-        <v>-11.17031192736994</v>
+        <v>-16.78154407027428</v>
       </c>
       <c r="F71">
-        <v>-2.216881132456558</v>
+        <v>-2.893423700936165</v>
       </c>
       <c r="G71">
-        <v>-7.046881354289611</v>
+        <v>-9.270445681742036</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.566415701862051</v>
       </c>
       <c r="E72">
-        <v>-11.17239502541347</v>
+        <v>-15.80365633610993</v>
       </c>
       <c r="F72">
-        <v>-2.297019880105591</v>
+        <v>-2.579629016714282</v>
       </c>
       <c r="G72">
-        <v>-7.036135323469137</v>
+        <v>-9.585672517445898</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.563237093181961</v>
       </c>
       <c r="E73">
-        <v>-12.74741639917725</v>
+        <v>-16.5635840878111</v>
       </c>
       <c r="F73">
-        <v>-2.064844236081543</v>
+        <v>-3.151866875302986</v>
       </c>
       <c r="G73">
-        <v>-6.716333313830001</v>
+        <v>-8.959648355969717</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.589029551394152</v>
       </c>
       <c r="E74">
-        <v>-14.2130207839677</v>
+        <v>-14.94316476212042</v>
       </c>
       <c r="F74">
-        <v>-2.687031820691654</v>
+        <v>-3.360243523844604</v>
       </c>
       <c r="G74">
-        <v>-6.246275573799964</v>
+        <v>-8.121186487238504</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.64009080587888</v>
       </c>
       <c r="E75">
-        <v>-14.5679580482149</v>
+        <v>-15.1899937663825</v>
       </c>
       <c r="F75">
-        <v>-2.101692503260273</v>
+        <v>-3.090499761368793</v>
       </c>
       <c r="G75">
-        <v>-6.946651277542636</v>
+        <v>-8.986573022840609</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.71154015358271</v>
       </c>
       <c r="E76">
-        <v>-13.09874899811434</v>
+        <v>-16.1938839982989</v>
       </c>
       <c r="F76">
-        <v>-2.244139390213079</v>
+        <v>-3.467748217012521</v>
       </c>
       <c r="G76">
-        <v>-6.622088703418028</v>
+        <v>-8.782616933257192</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-6.800579897384528</v>
       </c>
       <c r="E77">
-        <v>-14.00029118898338</v>
+        <v>-17.3154420988306</v>
       </c>
       <c r="F77">
-        <v>-2.441895540283405</v>
+        <v>-3.461104710442069</v>
       </c>
       <c r="G77">
-        <v>-4.978210831528607</v>
+        <v>-8.499025670726603</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.905824320310301</v>
       </c>
       <c r="E78">
-        <v>-13.51084918976036</v>
+        <v>-16.94000896122469</v>
       </c>
       <c r="F78">
-        <v>-2.927217777500774</v>
+        <v>-3.780929909356333</v>
       </c>
       <c r="G78">
-        <v>-7.063755204903276</v>
+        <v>-8.867552289612732</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.020595146315825</v>
       </c>
       <c r="E79">
-        <v>-12.87247926584708</v>
+        <v>-16.73412189046596</v>
       </c>
       <c r="F79">
-        <v>-2.578697103386132</v>
+        <v>-3.882374266605369</v>
       </c>
       <c r="G79">
-        <v>-6.368692926751134</v>
+        <v>-8.840150904184185</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.139196005525352</v>
       </c>
       <c r="E80">
-        <v>-15.10008544343422</v>
+        <v>-17.28370655298485</v>
       </c>
       <c r="F80">
-        <v>-2.853782178875195</v>
+        <v>-3.710771332176229</v>
       </c>
       <c r="G80">
-        <v>-5.63175224752721</v>
+        <v>-8.28976939773481</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.261641110346095</v>
       </c>
       <c r="E81">
-        <v>-15.78364953794404</v>
+        <v>-18.19425135018113</v>
       </c>
       <c r="F81">
-        <v>-3.346983846827992</v>
+        <v>-3.814350392222279</v>
       </c>
       <c r="G81">
-        <v>-6.438608337995001</v>
+        <v>-7.789294365289949</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.384686510026617</v>
       </c>
       <c r="E82">
-        <v>-16.24960687096328</v>
+        <v>-18.97428099800235</v>
       </c>
       <c r="F82">
-        <v>-3.206667520835187</v>
+        <v>-3.919032837648858</v>
       </c>
       <c r="G82">
-        <v>-6.274968071988827</v>
+        <v>-9.062007113498444</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.504859446137836</v>
       </c>
       <c r="E83">
-        <v>-17.80196323231867</v>
+        <v>-20.89077195431452</v>
       </c>
       <c r="F83">
-        <v>-3.523074047478098</v>
+        <v>-4.065093063212676</v>
       </c>
       <c r="G83">
-        <v>-4.566170402074297</v>
+        <v>-8.090620220274413</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.62155624690916</v>
       </c>
       <c r="E84">
-        <v>-17.99887939606821</v>
+        <v>-21.18575675117416</v>
       </c>
       <c r="F84">
-        <v>-3.842693811276467</v>
+        <v>-4.09220138646929</v>
       </c>
       <c r="G84">
-        <v>-5.183070700044247</v>
+        <v>-8.136163395258167</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.737689717853411</v>
       </c>
       <c r="E85">
-        <v>-18.60606624796467</v>
+        <v>-20.87309279178857</v>
       </c>
       <c r="F85">
-        <v>-2.8523043714286</v>
+        <v>-4.178844474965103</v>
       </c>
       <c r="G85">
-        <v>-5.577532132685026</v>
+        <v>-8.555013616886757</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.852347508954387</v>
       </c>
       <c r="E86">
-        <v>-19.52454493162239</v>
+        <v>-22.7456394363303</v>
       </c>
       <c r="F86">
-        <v>-3.678988531665618</v>
+        <v>-4.091239651914639</v>
       </c>
       <c r="G86">
-        <v>-5.805648583614047</v>
+        <v>-8.284416245597809</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.965159604294821</v>
       </c>
       <c r="E87">
-        <v>-19.75990331122305</v>
+        <v>-22.9949591012966</v>
       </c>
       <c r="F87">
-        <v>-3.945303681461242</v>
+        <v>-4.170809311157949</v>
       </c>
       <c r="G87">
-        <v>-6.45487966932052</v>
+        <v>-8.067820493145453</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.083207747412759</v>
       </c>
       <c r="E88">
-        <v>-21.28375745717416</v>
+        <v>-23.42814839639634</v>
       </c>
       <c r="F88">
-        <v>-4.080382240366146</v>
+        <v>-4.767416082002208</v>
       </c>
       <c r="G88">
-        <v>-4.355381346497822</v>
+        <v>-8.822631497190361</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.208602602677619</v>
       </c>
       <c r="E89">
-        <v>-23.90005161578765</v>
+        <v>-25.9643066789701</v>
       </c>
       <c r="F89">
-        <v>-4.044533812642594</v>
+        <v>-4.644035727559639</v>
       </c>
       <c r="G89">
-        <v>-6.099065545305192</v>
+        <v>-8.156198816861837</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.341638982902881</v>
       </c>
       <c r="E90">
-        <v>-24.13766517544413</v>
+        <v>-26.90045546820576</v>
       </c>
       <c r="F90">
-        <v>-4.591909052003674</v>
+        <v>-4.942076520515082</v>
       </c>
       <c r="G90">
-        <v>-6.819960010300267</v>
+        <v>-9.013769154445724</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.484485744276718</v>
       </c>
       <c r="E91">
-        <v>-28.30595794596641</v>
+        <v>-28.52698823380679</v>
       </c>
       <c r="F91">
-        <v>-4.322651541193307</v>
+        <v>-4.719907554716851</v>
       </c>
       <c r="G91">
-        <v>-6.514370172661223</v>
+        <v>-9.284247346095258</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.64147452055534</v>
       </c>
       <c r="E92">
-        <v>-28.86603508276107</v>
+        <v>-29.79119326558011</v>
       </c>
       <c r="F92">
-        <v>-4.376332233996923</v>
+        <v>-4.985944373065135</v>
       </c>
       <c r="G92">
-        <v>-8.250191825812824</v>
+        <v>-9.53270378881756</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.809714084508885</v>
       </c>
       <c r="E93">
-        <v>-29.23045497158033</v>
+        <v>-32.26224567734559</v>
       </c>
       <c r="F93">
-        <v>-4.321612768470196</v>
+        <v>-4.941717837429669</v>
       </c>
       <c r="G93">
-        <v>-7.683810452772152</v>
+        <v>-9.57908122127721</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.984719415328266</v>
       </c>
       <c r="E94">
-        <v>-32.32312648190471</v>
+        <v>-33.70199021131524</v>
       </c>
       <c r="F94">
-        <v>-4.706443270951748</v>
+        <v>-5.115273233827208</v>
       </c>
       <c r="G94">
-        <v>-6.6683668195115</v>
+        <v>-10.0187613954389</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.167634781829948</v>
       </c>
       <c r="E95">
-        <v>-33.35501174013653</v>
+        <v>-35.35427867283489</v>
       </c>
       <c r="F95">
-        <v>-3.916363837877038</v>
+        <v>-5.268961066436002</v>
       </c>
       <c r="G95">
-        <v>-7.911877245518083</v>
+        <v>-9.314025703221002</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.351250254422578</v>
       </c>
       <c r="E96">
-        <v>-36.10990210999177</v>
+        <v>-37.29766876475262</v>
       </c>
       <c r="F96">
-        <v>-4.903090237069725</v>
+        <v>-5.205252986221498</v>
       </c>
       <c r="G96">
-        <v>-7.335978054052006</v>
+        <v>-11.33971541324565</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.524770342267287</v>
       </c>
       <c r="E97">
-        <v>-36.92957854775015</v>
+        <v>-38.05367485796315</v>
       </c>
       <c r="F97">
-        <v>-5.152745261660246</v>
+        <v>-5.280235975155507</v>
       </c>
       <c r="G97">
-        <v>-8.531757034473378</v>
+        <v>-10.75009069997375</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.680539313398361</v>
       </c>
       <c r="E98">
-        <v>-38.91563365753114</v>
+        <v>-41.96343478315053</v>
       </c>
       <c r="F98">
-        <v>-4.96421795282451</v>
+        <v>-5.242097939930617</v>
       </c>
       <c r="G98">
-        <v>-8.29544698333466</v>
+        <v>-11.30154151263231</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.809444951638191</v>
       </c>
       <c r="E99">
-        <v>-41.18208508515607</v>
+        <v>-43.69873243746778</v>
       </c>
       <c r="F99">
-        <v>-5.413022441456865</v>
+        <v>-5.446999587217492</v>
       </c>
       <c r="G99">
-        <v>-9.231854652390751</v>
+        <v>-12.70438187435294</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.900121131638125</v>
       </c>
       <c r="E100">
-        <v>-43.6839243274627</v>
+        <v>-45.79850205805538</v>
       </c>
       <c r="F100">
-        <v>-4.778333136003703</v>
+        <v>-5.549754421697757</v>
       </c>
       <c r="G100">
-        <v>-8.681711505220205</v>
+        <v>-11.73829847508282</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.939043639168506</v>
       </c>
       <c r="E101">
-        <v>-46.30812067321958</v>
+        <v>-47.58143925893334</v>
       </c>
       <c r="F101">
-        <v>-5.137709564932032</v>
+        <v>-5.333591947937226</v>
       </c>
       <c r="G101">
-        <v>-8.416953936262532</v>
+        <v>-12.47207758331674</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.929897132698933</v>
       </c>
       <c r="E102">
-        <v>-48.09779397918394</v>
+        <v>-49.04301669821246</v>
       </c>
       <c r="F102">
-        <v>-5.67816627974493</v>
+        <v>-5.361531123698848</v>
       </c>
       <c r="G102">
-        <v>-8.851860303756586</v>
+        <v>-12.01070340423621</v>
       </c>
     </row>
   </sheetData>
